--- a/data/TCG_Match.xlsx
+++ b/data/TCG_Match.xlsx
@@ -20556,7 +20556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="54" min="1" max="1"/>
@@ -20972,7 +20972,9 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="54"/>
+    <row r="38" ht="15.75" customHeight="1" s="54">
+      <c r="G38" s="0" t="n"/>
+    </row>
     <row r="39" ht="15.75" customHeight="1" s="54"/>
     <row r="40" ht="15.75" customHeight="1" s="54"/>
     <row r="41" ht="15.75" customHeight="1" s="54"/>

--- a/data/TCG_Match.xlsx
+++ b/data/TCG_Match.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Match" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Liste" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Decklist" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -111,8 +112,11 @@
       <color theme="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -141,6 +145,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -184,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -340,6 +349,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21941,4 +21955,52 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="54" min="1" max="1"/>
+    <col width="26" customWidth="1" style="54" min="2" max="2"/>
+    <col width="13" customWidth="1" style="54" min="3" max="3"/>
+    <col width="60" customWidth="1" style="54" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="55" t="inlineStr">
+        <is>
+          <t>Nome lista</t>
+        </is>
+      </c>
+      <c r="B1" s="55" t="inlineStr">
+        <is>
+          <t>Mazzo</t>
+        </is>
+      </c>
+      <c r="C1" s="55" t="inlineStr">
+        <is>
+          <t>Aggiornata</t>
+        </is>
+      </c>
+      <c r="D1" s="55" t="inlineStr">
+        <is>
+          <t>Lista</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n"/>
+      <c r="B2" s="0" t="n"/>
+      <c r="C2" s="56" t="n"/>
+      <c r="D2" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/TCG_Match.xlsx
+++ b/data/TCG_Match.xlsx
@@ -14,9 +14,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -9589,16 +9590,50 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="54">
-      <c r="A122" s="44" t="n"/>
-      <c r="B122" s="42" t="n"/>
-      <c r="C122" s="44" t="n"/>
-      <c r="D122" s="44" t="n"/>
-      <c r="E122" s="44" t="n"/>
-      <c r="F122" s="44" t="n"/>
-      <c r="G122" s="44" t="n"/>
-      <c r="H122" s="44" t="n"/>
-      <c r="I122" s="44" t="n"/>
-      <c r="J122" s="44" t="n"/>
+      <c r="A122" s="44" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="42" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C122" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D122" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="E122" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult v1</t>
+        </is>
+      </c>
+      <c r="F122" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G122" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I122" s="44" t="inlineStr">
+        <is>
+          <t>Bad Draw</t>
+        </is>
+      </c>
+      <c r="J122" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
       <c r="K122" s="44" t="n"/>
       <c r="L122" s="25">
         <f>IF(D122="","",IF(H122="W",1,IF(H122="L",0,"")))</f>
@@ -9630,13 +9665,47 @@
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="54">
-      <c r="C123" s="50" t="n"/>
-      <c r="D123" s="50" t="n"/>
-      <c r="E123" s="50" t="n"/>
-      <c r="F123" s="50" t="n"/>
-      <c r="G123" s="50" t="n"/>
-      <c r="H123" s="50" t="n"/>
-      <c r="J123" s="50" t="n"/>
+      <c r="A123" s="48" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C123" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D123" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="E123" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult v1</t>
+        </is>
+      </c>
+      <c r="F123" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Blaziken ex</t>
+        </is>
+      </c>
+      <c r="G123" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I123" s="48" t="n"/>
+      <c r="J123" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K123" s="48" t="n"/>
       <c r="L123" s="25">
         <f>IF(D123="","",IF(H123="W",1,IF(H123="L",0,"")))</f>
         <v/>
@@ -9667,13 +9736,51 @@
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="54">
-      <c r="C124" s="50" t="n"/>
-      <c r="D124" s="50" t="n"/>
-      <c r="E124" s="50" t="n"/>
-      <c r="F124" s="50" t="n"/>
-      <c r="G124" s="50" t="n"/>
-      <c r="H124" s="50" t="n"/>
-      <c r="J124" s="50" t="n"/>
+      <c r="A124" s="44" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="42" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C124" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D124" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="E124" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult v1</t>
+        </is>
+      </c>
+      <c r="F124" s="44" t="inlineStr">
+        <is>
+          <t>MegaExcadrill ex</t>
+        </is>
+      </c>
+      <c r="G124" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I124" s="44" t="inlineStr">
+        <is>
+          <t>Bad Draw</t>
+        </is>
+      </c>
+      <c r="J124" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K124" s="44" t="n"/>
       <c r="L124" s="25">
         <f>IF(D124="","",IF(H124="W",1,IF(H124="L",0,"")))</f>
         <v/>
@@ -9704,13 +9811,51 @@
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="54">
-      <c r="C125" s="50" t="n"/>
-      <c r="D125" s="50" t="n"/>
-      <c r="E125" s="50" t="n"/>
-      <c r="F125" s="50" t="n"/>
-      <c r="G125" s="50" t="n"/>
-      <c r="H125" s="50" t="n"/>
-      <c r="J125" s="50" t="n"/>
+      <c r="A125" s="48" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C125" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D125" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E125" s="48" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="F125" s="48" t="inlineStr">
+        <is>
+          <t>MegaGreninja ex Dudunsparce</t>
+        </is>
+      </c>
+      <c r="G125" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I125" s="48" t="inlineStr">
+        <is>
+          <t>Bad Luck</t>
+        </is>
+      </c>
+      <c r="J125" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K125" s="48" t="n"/>
       <c r="L125" s="25">
         <f>IF(D125="","",IF(H125="W",1,IF(H125="L",0,"")))</f>
         <v/>
@@ -9741,13 +9886,47 @@
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="54">
-      <c r="C126" s="50" t="n"/>
-      <c r="D126" s="50" t="n"/>
-      <c r="E126" s="50" t="n"/>
-      <c r="F126" s="50" t="n"/>
-      <c r="G126" s="50" t="n"/>
-      <c r="H126" s="50" t="n"/>
-      <c r="J126" s="50" t="n"/>
+      <c r="A126" s="44" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="42" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C126" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D126" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E126" s="44" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="F126" s="44" t="inlineStr">
+        <is>
+          <t>MegaGreninja ex Drakloak</t>
+        </is>
+      </c>
+      <c r="G126" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I126" s="44" t="n"/>
+      <c r="J126" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K126" s="44" t="n"/>
       <c r="L126" s="25">
         <f>IF(D126="","",IF(H126="W",1,IF(H126="L",0,"")))</f>
         <v/>
@@ -9778,13 +9957,47 @@
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="54">
-      <c r="C127" s="50" t="n"/>
-      <c r="D127" s="50" t="n"/>
-      <c r="E127" s="50" t="n"/>
-      <c r="F127" s="50" t="n"/>
-      <c r="G127" s="50" t="n"/>
-      <c r="H127" s="50" t="n"/>
-      <c r="J127" s="50" t="n"/>
+      <c r="A127" s="48" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C127" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D127" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E127" s="48" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="F127" s="48" t="inlineStr">
+        <is>
+          <t>MegaLucario ex</t>
+        </is>
+      </c>
+      <c r="G127" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I127" s="48" t="n"/>
+      <c r="J127" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K127" s="48" t="n"/>
       <c r="L127" s="25">
         <f>IF(D127="","",IF(H127="W",1,IF(H127="L",0,"")))</f>
         <v/>
@@ -9815,13 +10028,51 @@
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="54">
-      <c r="C128" s="50" t="n"/>
-      <c r="D128" s="50" t="n"/>
-      <c r="E128" s="50" t="n"/>
-      <c r="F128" s="50" t="n"/>
-      <c r="G128" s="50" t="n"/>
-      <c r="H128" s="50" t="n"/>
-      <c r="J128" s="50" t="n"/>
+      <c r="A128" s="44" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="42" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C128" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D128" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E128" s="44" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="F128" s="44" t="inlineStr">
+        <is>
+          <t>MegaGreninja ex Blaziken</t>
+        </is>
+      </c>
+      <c r="G128" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I128" s="44" t="inlineStr">
+        <is>
+          <t>Bad Start</t>
+        </is>
+      </c>
+      <c r="J128" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K128" s="44" t="n"/>
       <c r="L128" s="25">
         <f>IF(D128="","",IF(H128="W",1,IF(H128="L",0,"")))</f>
         <v/>
@@ -9852,13 +10103,51 @@
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="54">
-      <c r="C129" s="50" t="n"/>
-      <c r="D129" s="50" t="n"/>
-      <c r="E129" s="50" t="n"/>
-      <c r="F129" s="50" t="n"/>
-      <c r="G129" s="50" t="n"/>
-      <c r="H129" s="50" t="n"/>
-      <c r="J129" s="50" t="n"/>
+      <c r="A129" s="48" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C129" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D129" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E129" s="48" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="F129" s="48" t="inlineStr">
+        <is>
+          <t>MegaSharpedo ex</t>
+        </is>
+      </c>
+      <c r="G129" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I129" s="48" t="n"/>
+      <c r="J129" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K129" s="48" t="inlineStr">
+        <is>
+          <t>Boss su toxtricity per guadagnare tempo sui brutti start</t>
+        </is>
+      </c>
       <c r="L129" s="25">
         <f>IF(D129="","",IF(H129="W",1,IF(H129="L",0,"")))</f>
         <v/>
@@ -9889,13 +10178,47 @@
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="54">
-      <c r="C130" s="50" t="n"/>
-      <c r="D130" s="50" t="n"/>
-      <c r="E130" s="50" t="n"/>
-      <c r="F130" s="50" t="n"/>
-      <c r="G130" s="50" t="n"/>
-      <c r="H130" s="50" t="n"/>
-      <c r="J130" s="50" t="n"/>
+      <c r="A130" s="44" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C130" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D130" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E130" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F130" s="44" t="inlineStr">
+        <is>
+          <t>Area Della Festa</t>
+        </is>
+      </c>
+      <c r="G130" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I130" s="44" t="n"/>
+      <c r="J130" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K130" s="44" t="n"/>
       <c r="L130" s="25">
         <f>IF(D130="","",IF(H130="W",1,IF(H130="L",0,"")))</f>
         <v/>
@@ -9926,13 +10249,47 @@
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="54">
-      <c r="C131" s="50" t="n"/>
-      <c r="D131" s="50" t="n"/>
-      <c r="E131" s="50" t="n"/>
-      <c r="F131" s="50" t="n"/>
-      <c r="G131" s="50" t="n"/>
-      <c r="H131" s="50" t="n"/>
-      <c r="J131" s="50" t="n"/>
+      <c r="A131" s="48" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C131" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D131" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E131" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F131" s="48" t="inlineStr">
+        <is>
+          <t>Area Della Festa</t>
+        </is>
+      </c>
+      <c r="G131" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I131" s="48" t="n"/>
+      <c r="J131" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K131" s="48" t="n"/>
       <c r="L131" s="25">
         <f>IF(D131="","",IF(H131="W",1,IF(H131="L",0,"")))</f>
         <v/>
@@ -9963,13 +10320,47 @@
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="54">
-      <c r="C132" s="50" t="n"/>
-      <c r="D132" s="50" t="n"/>
-      <c r="E132" s="50" t="n"/>
-      <c r="F132" s="50" t="n"/>
-      <c r="G132" s="50" t="n"/>
-      <c r="H132" s="50" t="n"/>
-      <c r="J132" s="50" t="n"/>
+      <c r="A132" s="44" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C132" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D132" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E132" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F132" s="44" t="inlineStr">
+        <is>
+          <t>Crusle</t>
+        </is>
+      </c>
+      <c r="G132" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I132" s="44" t="n"/>
+      <c r="J132" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K132" s="44" t="n"/>
       <c r="L132" s="25">
         <f>IF(D132="","",IF(H132="W",1,IF(H132="L",0,"")))</f>
         <v/>
@@ -10000,13 +10391,47 @@
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="54">
-      <c r="C133" s="50" t="n"/>
-      <c r="D133" s="50" t="n"/>
-      <c r="E133" s="50" t="n"/>
-      <c r="F133" s="50" t="n"/>
-      <c r="G133" s="50" t="n"/>
-      <c r="H133" s="50" t="n"/>
-      <c r="J133" s="50" t="n"/>
+      <c r="A133" s="48" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C133" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D133" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E133" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F133" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dudunsparce</t>
+        </is>
+      </c>
+      <c r="G133" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I133" s="48" t="n"/>
+      <c r="J133" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K133" s="48" t="n"/>
       <c r="L133" s="25">
         <f>IF(D133="","",IF(H133="W",1,IF(H133="L",0,"")))</f>
         <v/>
@@ -10037,13 +10462,47 @@
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="54">
-      <c r="C134" s="50" t="n"/>
-      <c r="D134" s="50" t="n"/>
-      <c r="E134" s="50" t="n"/>
-      <c r="F134" s="50" t="n"/>
-      <c r="G134" s="50" t="n"/>
-      <c r="H134" s="50" t="n"/>
-      <c r="J134" s="50" t="n"/>
+      <c r="A134" s="44" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C134" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D134" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E134" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F134" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G134" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I134" s="44" t="n"/>
+      <c r="J134" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K134" s="44" t="n"/>
       <c r="L134" s="25">
         <f>IF(D134="","",IF(H134="W",1,IF(H134="L",0,"")))</f>
         <v/>
@@ -10074,13 +10533,47 @@
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="54">
-      <c r="C135" s="50" t="n"/>
-      <c r="D135" s="50" t="n"/>
-      <c r="E135" s="50" t="n"/>
-      <c r="F135" s="50" t="n"/>
-      <c r="G135" s="50" t="n"/>
-      <c r="H135" s="50" t="n"/>
-      <c r="J135" s="50" t="n"/>
+      <c r="A135" s="48" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C135" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D135" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E135" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F135" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G135" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I135" s="48" t="n"/>
+      <c r="J135" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K135" s="48" t="n"/>
       <c r="L135" s="25">
         <f>IF(D135="","",IF(H135="W",1,IF(H135="L",0,"")))</f>
         <v/>
@@ -10111,13 +10604,47 @@
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="54">
-      <c r="C136" s="50" t="n"/>
-      <c r="D136" s="50" t="n"/>
-      <c r="E136" s="50" t="n"/>
-      <c r="F136" s="50" t="n"/>
-      <c r="G136" s="50" t="n"/>
-      <c r="H136" s="50" t="n"/>
-      <c r="J136" s="50" t="n"/>
+      <c r="A136" s="44" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C136" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D136" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E136" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F136" s="44" t="inlineStr">
+        <is>
+          <t>MegaGreninja ex Drakloak</t>
+        </is>
+      </c>
+      <c r="G136" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I136" s="44" t="n"/>
+      <c r="J136" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K136" s="44" t="n"/>
       <c r="L136" s="25">
         <f>IF(D136="","",IF(H136="W",1,IF(H136="L",0,"")))</f>
         <v/>
@@ -10148,13 +10675,47 @@
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="54">
-      <c r="C137" s="50" t="n"/>
-      <c r="D137" s="50" t="n"/>
-      <c r="E137" s="50" t="n"/>
-      <c r="F137" s="50" t="n"/>
-      <c r="G137" s="50" t="n"/>
-      <c r="H137" s="50" t="n"/>
-      <c r="J137" s="50" t="n"/>
+      <c r="A137" s="48" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C137" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D137" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E137" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F137" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="G137" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I137" s="48" t="n"/>
+      <c r="J137" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K137" s="48" t="n"/>
       <c r="L137" s="25">
         <f>IF(D137="","",IF(H137="W",1,IF(H137="L",0,"")))</f>
         <v/>
@@ -10185,13 +10746,51 @@
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="54">
-      <c r="C138" s="50" t="n"/>
-      <c r="D138" s="50" t="n"/>
-      <c r="E138" s="50" t="n"/>
-      <c r="F138" s="50" t="n"/>
-      <c r="G138" s="50" t="n"/>
-      <c r="H138" s="50" t="n"/>
-      <c r="J138" s="50" t="n"/>
+      <c r="A138" s="44" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C138" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D138" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E138" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F138" s="44" t="inlineStr">
+        <is>
+          <t>Slowking</t>
+        </is>
+      </c>
+      <c r="G138" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I138" s="44" t="n"/>
+      <c r="J138" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K138" s="44" t="inlineStr">
+        <is>
+          <t>Esplodi su quello che sta cercando di caricare e vai di budew</t>
+        </is>
+      </c>
       <c r="L138" s="25">
         <f>IF(D138="","",IF(H138="W",1,IF(H138="L",0,"")))</f>
         <v/>
@@ -10222,13 +10821,47 @@
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="54">
-      <c r="C139" s="50" t="n"/>
-      <c r="D139" s="50" t="n"/>
-      <c r="E139" s="50" t="n"/>
-      <c r="F139" s="50" t="n"/>
-      <c r="G139" s="50" t="n"/>
-      <c r="H139" s="50" t="n"/>
-      <c r="J139" s="50" t="n"/>
+      <c r="A139" s="48" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C139" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D139" s="48" t="inlineStr">
+        <is>
+          <t>Basic Box</t>
+        </is>
+      </c>
+      <c r="E139" s="48" t="inlineStr">
+        <is>
+          <t>BB v1</t>
+        </is>
+      </c>
+      <c r="F139" s="48" t="inlineStr">
+        <is>
+          <t>Slowking</t>
+        </is>
+      </c>
+      <c r="G139" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I139" s="48" t="n"/>
+      <c r="J139" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K139" s="48" t="n"/>
       <c r="L139" s="25">
         <f>IF(D139="","",IF(H139="W",1,IF(H139="L",0,"")))</f>
         <v/>
@@ -10259,13 +10892,51 @@
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="54">
-      <c r="C140" s="50" t="n"/>
-      <c r="D140" s="50" t="n"/>
-      <c r="E140" s="50" t="n"/>
-      <c r="F140" s="50" t="n"/>
-      <c r="G140" s="50" t="n"/>
-      <c r="H140" s="50" t="n"/>
-      <c r="J140" s="50" t="n"/>
+      <c r="A140" s="44" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="42" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C140" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D140" s="44" t="inlineStr">
+        <is>
+          <t>Basic Box</t>
+        </is>
+      </c>
+      <c r="E140" s="44" t="inlineStr">
+        <is>
+          <t>BB v1</t>
+        </is>
+      </c>
+      <c r="F140" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="G140" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I140" s="44" t="n"/>
+      <c r="J140" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K140" s="44" t="inlineStr">
+        <is>
+          <t>forte peach su fez</t>
+        </is>
+      </c>
       <c r="L140" s="25">
         <f>IF(D140="","",IF(H140="W",1,IF(H140="L",0,"")))</f>
         <v/>
@@ -10296,13 +10967,47 @@
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="54">
-      <c r="C141" s="50" t="n"/>
-      <c r="D141" s="50" t="n"/>
-      <c r="E141" s="50" t="n"/>
-      <c r="F141" s="50" t="n"/>
-      <c r="G141" s="50" t="n"/>
-      <c r="H141" s="50" t="n"/>
-      <c r="J141" s="50" t="n"/>
+      <c r="A141" s="48" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="24" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C141" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D141" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E141" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F141" s="48" t="inlineStr">
+        <is>
+          <t>Garchomp ex</t>
+        </is>
+      </c>
+      <c r="G141" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I141" s="48" t="n"/>
+      <c r="J141" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K141" s="48" t="n"/>
       <c r="L141" s="25">
         <f>IF(D141="","",IF(H141="W",1,IF(H141="L",0,"")))</f>
         <v/>
@@ -10333,13 +11038,47 @@
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="54">
-      <c r="C142" s="50" t="n"/>
-      <c r="D142" s="50" t="n"/>
-      <c r="E142" s="50" t="n"/>
-      <c r="F142" s="50" t="n"/>
-      <c r="G142" s="50" t="n"/>
-      <c r="H142" s="50" t="n"/>
-      <c r="J142" s="50" t="n"/>
+      <c r="A142" s="44" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="42" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C142" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E142" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F142" s="44" t="inlineStr">
+        <is>
+          <t>Pikachu ex box</t>
+        </is>
+      </c>
+      <c r="G142" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I142" s="44" t="n"/>
+      <c r="J142" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K142" s="44" t="n"/>
       <c r="L142" s="25">
         <f>IF(D142="","",IF(H142="W",1,IF(H142="L",0,"")))</f>
         <v/>
@@ -10370,13 +11109,47 @@
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="54">
-      <c r="C143" s="50" t="n"/>
-      <c r="D143" s="50" t="n"/>
-      <c r="E143" s="50" t="n"/>
-      <c r="F143" s="50" t="n"/>
-      <c r="G143" s="50" t="n"/>
-      <c r="H143" s="50" t="n"/>
-      <c r="J143" s="50" t="n"/>
+      <c r="A143" s="48" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="24" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C143" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D143" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E143" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F143" s="48" t="inlineStr">
+        <is>
+          <t>Raging Bolt</t>
+        </is>
+      </c>
+      <c r="G143" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I143" s="48" t="n"/>
+      <c r="J143" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K143" s="48" t="n"/>
       <c r="L143" s="25">
         <f>IF(D143="","",IF(H143="W",1,IF(H143="L",0,"")))</f>
         <v/>
@@ -10407,13 +11180,47 @@
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="54">
-      <c r="C144" s="50" t="n"/>
-      <c r="D144" s="50" t="n"/>
-      <c r="E144" s="50" t="n"/>
-      <c r="F144" s="50" t="n"/>
-      <c r="G144" s="50" t="n"/>
-      <c r="H144" s="50" t="n"/>
-      <c r="J144" s="50" t="n"/>
+      <c r="A144" s="44" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="42" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C144" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D144" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E144" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F144" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G144" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I144" s="44" t="n"/>
+      <c r="J144" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K144" s="44" t="n"/>
       <c r="L144" s="25">
         <f>IF(D144="","",IF(H144="W",1,IF(H144="L",0,"")))</f>
         <v/>
@@ -10444,13 +11251,47 @@
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="54">
-      <c r="C145" s="50" t="n"/>
-      <c r="D145" s="50" t="n"/>
-      <c r="E145" s="50" t="n"/>
-      <c r="F145" s="50" t="n"/>
-      <c r="G145" s="50" t="n"/>
-      <c r="H145" s="50" t="n"/>
-      <c r="J145" s="50" t="n"/>
+      <c r="A145" s="48" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="24" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C145" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D145" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E145" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F145" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G145" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I145" s="48" t="n"/>
+      <c r="J145" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K145" s="48" t="n"/>
       <c r="L145" s="25">
         <f>IF(D145="","",IF(H145="W",1,IF(H145="L",0,"")))</f>
         <v/>
@@ -10481,13 +11322,47 @@
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="54">
-      <c r="C146" s="50" t="n"/>
-      <c r="D146" s="50" t="n"/>
-      <c r="E146" s="50" t="n"/>
-      <c r="F146" s="50" t="n"/>
-      <c r="G146" s="50" t="n"/>
-      <c r="H146" s="50" t="n"/>
-      <c r="J146" s="50" t="n"/>
+      <c r="A146" s="44" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="42" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C146" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D146" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E146" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F146" s="44" t="inlineStr">
+        <is>
+          <t>Slowking</t>
+        </is>
+      </c>
+      <c r="G146" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I146" s="44" t="n"/>
+      <c r="J146" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K146" s="44" t="n"/>
       <c r="L146" s="25">
         <f>IF(D146="","",IF(H146="W",1,IF(H146="L",0,"")))</f>
         <v/>
@@ -10518,13 +11393,47 @@
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="54">
-      <c r="C147" s="50" t="n"/>
-      <c r="D147" s="50" t="n"/>
-      <c r="E147" s="50" t="n"/>
-      <c r="F147" s="50" t="n"/>
-      <c r="G147" s="50" t="n"/>
-      <c r="H147" s="50" t="n"/>
-      <c r="J147" s="50" t="n"/>
+      <c r="A147" s="48" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="24" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C147" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D147" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E147" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F147" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G147" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I147" s="48" t="n"/>
+      <c r="J147" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K147" s="48" t="n"/>
       <c r="L147" s="25">
         <f>IF(D147="","",IF(H147="W",1,IF(H147="L",0,"")))</f>
         <v/>
@@ -10555,13 +11464,47 @@
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="54">
-      <c r="C148" s="50" t="n"/>
-      <c r="D148" s="50" t="n"/>
-      <c r="E148" s="50" t="n"/>
-      <c r="F148" s="50" t="n"/>
-      <c r="G148" s="50" t="n"/>
-      <c r="H148" s="50" t="n"/>
-      <c r="J148" s="50" t="n"/>
+      <c r="A148" s="44" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="42" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C148" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D148" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E148" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F148" s="44" t="inlineStr">
+        <is>
+          <t>Area Della Festa</t>
+        </is>
+      </c>
+      <c r="G148" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I148" s="44" t="n"/>
+      <c r="J148" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K148" s="44" t="n"/>
       <c r="L148" s="25">
         <f>IF(D148="","",IF(H148="W",1,IF(H148="L",0,"")))</f>
         <v/>
@@ -10592,13 +11535,47 @@
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="54">
-      <c r="C149" s="50" t="n"/>
-      <c r="D149" s="50" t="n"/>
-      <c r="E149" s="50" t="n"/>
-      <c r="F149" s="50" t="n"/>
-      <c r="G149" s="50" t="n"/>
-      <c r="H149" s="50" t="n"/>
-      <c r="J149" s="50" t="n"/>
+      <c r="A149" s="48" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="24" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C149" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D149" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E149" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F149" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G149" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I149" s="48" t="n"/>
+      <c r="J149" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K149" s="48" t="n"/>
       <c r="L149" s="25">
         <f>IF(D149="","",IF(H149="W",1,IF(H149="L",0,"")))</f>
         <v/>
@@ -10629,13 +11606,47 @@
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="54">
-      <c r="C150" s="50" t="n"/>
-      <c r="D150" s="50" t="n"/>
-      <c r="E150" s="50" t="n"/>
-      <c r="F150" s="50" t="n"/>
-      <c r="G150" s="50" t="n"/>
-      <c r="H150" s="50" t="n"/>
-      <c r="J150" s="50" t="n"/>
+      <c r="A150" s="44" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="42" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C150" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D150" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E150" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F150" s="44" t="inlineStr">
+        <is>
+          <t>Toxtricity box</t>
+        </is>
+      </c>
+      <c r="G150" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I150" s="44" t="n"/>
+      <c r="J150" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K150" s="44" t="n"/>
       <c r="L150" s="25">
         <f>IF(D150="","",IF(H150="W",1,IF(H150="L",0,"")))</f>
         <v/>
@@ -20538,10 +21549,10 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Liste!$F$2:$F$9</formula1>
+      <formula1>Liste!$F$2:$F$12</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F113 F116:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Liste!$G$2:$G$37</formula1>
+      <formula1>Liste!$G$2:$G$42</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Liste!$C$2:$C$3</formula1>
@@ -20553,7 +21564,7 @@
       <formula1>"W,L"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Liste!$A$2:$A$6</formula1>
+      <formula1>Liste!$A$2:$A$9</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2"</formula1>
@@ -20570,7 +21581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="54" min="1" max="1"/>
@@ -20641,7 +21652,7 @@
     <row r="2">
       <c r="A2" s="50" t="inlineStr">
         <is>
-          <t>Area Della Festa</t>
+          <t>Alakazam Dusknoir</t>
         </is>
       </c>
       <c r="B2" s="50" t="inlineStr">
@@ -20664,7 +21675,7 @@
       </c>
       <c r="F2" s="50" t="inlineStr">
         <is>
-          <t>Bolt v1</t>
+          <t>BB v1</t>
         </is>
       </c>
       <c r="G2" s="50" t="inlineStr">
@@ -20676,7 +21687,7 @@
     <row r="3">
       <c r="A3" s="50" t="inlineStr">
         <is>
-          <t>Dragapult ex</t>
+          <t>Area Della Festa</t>
         </is>
       </c>
       <c r="C3" s="50" t="inlineStr">
@@ -20694,7 +21705,7 @@
       </c>
       <c r="F3" s="50" t="inlineStr">
         <is>
-          <t>Dragapolli v1</t>
+          <t>Bolt v1</t>
         </is>
       </c>
       <c r="G3" s="50" t="inlineStr">
@@ -20706,12 +21717,12 @@
     <row r="4">
       <c r="A4" s="50" t="inlineStr">
         <is>
-          <t>Dragapult ex Blaziken ex</t>
+          <t>Basic Box</t>
         </is>
       </c>
       <c r="F4" s="50" t="inlineStr">
         <is>
-          <t>Dragapolli v2</t>
+          <t>Dragapolli v1</t>
         </is>
       </c>
       <c r="G4" s="50" t="inlineStr">
@@ -20723,12 +21734,12 @@
     <row r="5">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>Grimmsnarl ex Froslass</t>
+          <t>Dragapult ex</t>
         </is>
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>Dragapolli v3</t>
+          <t>Dragapolli v2</t>
         </is>
       </c>
       <c r="G5" s="50" t="inlineStr">
@@ -20740,259 +21751,317 @@
     <row r="6">
       <c r="A6" s="50" t="inlineStr">
         <is>
+          <t>Dragapult ex Blaziken ex</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
+        <is>
+          <t>Dragapolli v3</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>Clafairy ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>Dragapult v1</t>
+        </is>
+      </c>
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>Crusle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Grimmsnarl ex Froslass</t>
+        </is>
+      </c>
+      <c r="F8" s="50" t="inlineStr">
+        <is>
+          <t>Dragapult v2</t>
+        </is>
+      </c>
+      <c r="G8" s="50" t="inlineStr">
+        <is>
+          <t>Dhelmise Banette</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
           <t>Ragingbolt ex Ogerpon ex</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
-        <is>
-          <t>Dragapult v1</t>
-        </is>
-      </c>
-      <c r="G6" s="50" t="inlineStr">
-        <is>
-          <t>Clafairy ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="F7" s="50" t="inlineStr">
-        <is>
-          <t>Dragapult v2</t>
-        </is>
-      </c>
-      <c r="G7" s="50" t="inlineStr">
-        <is>
-          <t>Dhelmise Banette</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>Grimmsnarl v1</t>
         </is>
       </c>
-      <c r="G8" s="50" t="inlineStr">
+      <c r="G9" s="50" t="inlineStr">
         <is>
           <t>Doublade</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" s="50" t="inlineStr">
+    <row r="10">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>Mele v1</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G10" s="50" t="inlineStr">
         <is>
           <t>Dragapult ex</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="G10" s="50" t="inlineStr">
+    <row r="11">
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>Dragapult ex Blaziken ex</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="G11" s="50" t="inlineStr">
+    <row r="12">
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="G12" s="50" t="inlineStr">
         <is>
           <t>Dragapult ex Dusknoir</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="G12" s="50" t="inlineStr">
-        <is>
-          <t>Garchomp ex</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="G13" s="50" t="inlineStr">
         <is>
-          <t>Grimmsnarl ex Froslass</t>
+          <t>Garchomp ex</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="G14" s="50" t="inlineStr">
         <is>
-          <t>Honchkrow Porygon2</t>
+          <t>Grimmsnarl ex Froslass</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="G15" s="50" t="inlineStr">
         <is>
-          <t>Hydraigon ex</t>
+          <t>Honchkrow Porygon2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="G16" s="50" t="inlineStr">
         <is>
-          <t>Hydrapple ex Ogerpon ex</t>
+          <t>Hydraigon ex</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="50" t="inlineStr">
         <is>
-          <t>MegaChandelure ex</t>
+          <t>Hydrapple ex Ogerpon ex</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="G18" s="50" t="inlineStr">
         <is>
-          <t>MegaCharizard ex Oricorio</t>
+          <t>MegaChandelure ex</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="G19" s="50" t="inlineStr">
         <is>
-          <t>MegaDarkrai ex</t>
+          <t>MegaCharizard ex Oricorio</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="G20" s="50" t="inlineStr">
         <is>
-          <t>MegaExcadrill ex</t>
+          <t>MegaDarkrai ex</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="54">
       <c r="G21" s="50" t="inlineStr">
         <is>
-          <t>MegaFroslass ex Chandelure</t>
+          <t>MegaExcadrill ex</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="54">
       <c r="G22" s="50" t="inlineStr">
         <is>
-          <t>MegaGreninja ex Blaziken</t>
+          <t>MegaFroslass ex Chandelure</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="54">
       <c r="G23" s="50" t="inlineStr">
         <is>
-          <t>MegaKangaskhan ex Bouffalant</t>
+          <t>MegaGreninja ex Blaziken</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="54">
       <c r="G24" s="50" t="inlineStr">
         <is>
-          <t>MegaLopunny ex</t>
+          <t>MegaGreninja ex Drakloak</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="54">
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>MegaLucario ex</t>
+          <t>MegaGreninja ex Dudunsparce</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="54">
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>MegaStarmie ex Dragapult</t>
+          <t>MegaKangaskhan ex Bouffalant</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="54">
       <c r="G27" s="50" t="inlineStr">
         <is>
-          <t>MegaStarmie ex Dusknoir</t>
+          <t>MegaLopunny ex</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="54">
       <c r="G28" s="50" t="inlineStr">
         <is>
-          <t>Metagross ex</t>
+          <t>MegaLucario ex</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="54">
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>Mewtwo ex Spidops</t>
+          <t>MegaSharpedo ex</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="54">
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>Raging Bolt</t>
+          <t>MegaStarmie ex Dragapult</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="54">
       <c r="G31" s="50" t="inlineStr">
         <is>
-          <t>Slowking</t>
+          <t>MegaStarmie ex Dusknoir</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="54">
       <c r="G32" s="50" t="inlineStr">
         <is>
-          <t>Spineferree ex Bastiodon</t>
+          <t>Metagross ex</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="54">
       <c r="G33" s="50" t="inlineStr">
         <is>
-          <t>Toucannon Dusknoir</t>
+          <t>Mewtwo ex Spidops</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="54">
       <c r="G34" s="50" t="inlineStr">
         <is>
-          <t>Toxtricity box</t>
+          <t>Pikachu ex box</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="54">
       <c r="G35" s="50" t="inlineStr">
         <is>
-          <t>Typhlosion</t>
+          <t>Raging Bolt</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="54">
       <c r="G36" s="50" t="inlineStr">
         <is>
-          <t>Vileplume ex Ogerpon</t>
+          <t>Slowking</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="54">
       <c r="G37" s="50" t="inlineStr">
         <is>
+          <t>Spineferree ex Bastiodon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="54">
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>Toucannon Dusknoir</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="54">
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>Toxtricity box</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="54">
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>Typhlosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="54">
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>Vileplume ex Ogerpon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="54">
+      <c r="G42" s="0" t="inlineStr">
+        <is>
           <t>Zoroark ex</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="54">
-      <c r="G38" s="0" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="54"/>
-    <row r="40" ht="15.75" customHeight="1" s="54"/>
-    <row r="41" ht="15.75" customHeight="1" s="54"/>
-    <row r="42" ht="15.75" customHeight="1" s="54"/>
     <row r="43" ht="15.75" customHeight="1" s="54"/>
     <row r="44" ht="15.75" customHeight="1" s="54"/>
     <row r="45" ht="15.75" customHeight="1" s="54"/>
@@ -21963,7 +23032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="54" min="1" max="1"/>
@@ -21995,10 +23064,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="n"/>
-      <c r="B2" s="0" t="n"/>
-      <c r="C2" s="56" t="n"/>
-      <c r="D2" s="57" t="n"/>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>BB v1</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Basic Box</t>
+        </is>
+      </c>
+      <c r="C2" s="56" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D2" s="57" t="inlineStr">
+        <is>
+          <t>Pokémon: 12
+3 Meowth ex POR 62
+2 Mega Kangaskhan ex MEG 104
+2 Latias ex SSP 76
+2 Lillie's Clefairy ex JTG 56
+2 Teal Mask Ogerpon ex TWM 25
+2 Wellspring Mask Ogerpon ex TWM 64
+1 Iron Leaves ex TEF 25
+1 Chien-Pao SSP 56
+1 Fezandipiti ex ASC 142
+1 Paldean Tauros SSP 18
+1 Pecharunt PR-SV 149
+1 Moltres PFL 14
+Carte Allenatore: 12
+4 Crispin SCR 133
+3 Boss's Orders MEG 114
+2 Cyrano SSP 170
+2 Ciphermaniac's Codebreaking TEF 145
+1 Brock's Scouting JTG 146
+4 Ultra Ball MEG 131
+4 Energy Switch MEG 115
+2 Night Stretcher ASC 196
+1 Tool Scrapper ASC 212
+1 Unfair Stamp TWM 165
+2 Lillie's Pearl JTG 151
+3 Area Zero Underdepths SCR 131
+Energia: 5
+5 Basic {G} Energy MEE 1
+3 Prism Energy ASC 216
+2 Basic {P} Energy MEE 5
+1 Basic {W} Energy MEE 3
+1 Basic {R} Energy MEE 2
+Totale carte: 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>PultNoir v1</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D3" s="57" t="inlineStr">
+        <is>
+          <t>Pokémon: 11
+1 Meowth ex POR 62
+1 Dusknoir PRE 37
+4 Drakloak TWM 129
+4 Dreepy TWM 128
+1 Munkidori TWM 95
+3 Dragapult ex TWM 130
+2 Duskull PRE 35
+1 Fezandipiti ex ASC 142
+2 Dusclops PRE 36
+2 Budew ASC 16
+1 Moltres PFL 14
+Carte Allenatore: 12
+3 Night Stretcher ASC 196
+2 Crispin SCR 133
+4 Buddy-Buddy Poffin TEF 144
+4 Lillie's Determination MEG 119
+1 Jamming Tower ASC 261
+1 Rosa's Encouragement POR 84
+4 Poké Pad POR 81
+3 Boss's Orders MEG 114
+3 Crushing Hammer POR 71
+3 Ultra Ball MEG 131
+1 Unfair Stamp TWM 165
+1 Dawn PFL 118
+Energia: 3
+3 Basic {P} Energy MEE 5
+2 Basic {D} Energy MEE 7
+3 Basic {R} Energy MEE 2
+Totale carte: 60</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/TCG_Match.xlsx
+++ b/data/TCG_Match.xlsx
@@ -11416,11 +11416,11 @@
       </c>
       <c r="F147" s="48" t="inlineStr">
         <is>
-          <t>Dragapult ex</t>
+          <t>MegaExcadrill ex</t>
         </is>
       </c>
       <c r="G147" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
@@ -11487,15 +11487,15 @@
       </c>
       <c r="F148" s="44" t="inlineStr">
         <is>
-          <t>Area Della Festa</t>
+          <t>Dragapult ex</t>
         </is>
       </c>
       <c r="G148" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="44" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I148" s="44" t="n"/>
@@ -11562,11 +11562,11 @@
         </is>
       </c>
       <c r="G149" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I149" s="48" t="n"/>
@@ -11629,11 +11629,11 @@
       </c>
       <c r="F150" s="44" t="inlineStr">
         <is>
-          <t>Toxtricity box</t>
+          <t>Area Della Festa</t>
         </is>
       </c>
       <c r="G150" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" s="44" t="inlineStr">
         <is>
@@ -11677,13 +11677,47 @@
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="54">
-      <c r="C151" s="50" t="n"/>
-      <c r="D151" s="50" t="n"/>
-      <c r="E151" s="50" t="n"/>
-      <c r="F151" s="50" t="n"/>
-      <c r="G151" s="50" t="n"/>
-      <c r="H151" s="50" t="n"/>
-      <c r="J151" s="50" t="n"/>
+      <c r="A151" s="48" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="24" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C151" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D151" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E151" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F151" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex</t>
+        </is>
+      </c>
+      <c r="G151" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I151" s="48" t="n"/>
+      <c r="J151" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K151" s="48" t="n"/>
       <c r="L151" s="25">
         <f>IF(D151="","",IF(H151="W",1,IF(H151="L",0,"")))</f>
         <v/>
@@ -11714,13 +11748,47 @@
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="54">
-      <c r="C152" s="50" t="n"/>
-      <c r="D152" s="50" t="n"/>
-      <c r="E152" s="50" t="n"/>
-      <c r="F152" s="50" t="n"/>
-      <c r="G152" s="50" t="n"/>
-      <c r="H152" s="50" t="n"/>
-      <c r="J152" s="50" t="n"/>
+      <c r="A152" s="44" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="42" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C152" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E152" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F152" s="44" t="inlineStr">
+        <is>
+          <t>Toxtricity box</t>
+        </is>
+      </c>
+      <c r="G152" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I152" s="44" t="n"/>
+      <c r="J152" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K152" s="44" t="n"/>
       <c r="L152" s="25">
         <f>IF(D152="","",IF(H152="W",1,IF(H152="L",0,"")))</f>
         <v/>
@@ -11751,13 +11819,51 @@
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="54">
-      <c r="C153" s="50" t="n"/>
-      <c r="D153" s="50" t="n"/>
-      <c r="E153" s="50" t="n"/>
-      <c r="F153" s="50" t="n"/>
-      <c r="G153" s="50" t="n"/>
-      <c r="H153" s="50" t="n"/>
-      <c r="J153" s="50" t="n"/>
+      <c r="A153" s="48" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C153" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D153" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E153" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F153" s="48" t="inlineStr">
+        <is>
+          <t>MegaMagnetric ex Eelektrik</t>
+        </is>
+      </c>
+      <c r="G153" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I153" s="48" t="inlineStr">
+        <is>
+          <t>Bad Opening</t>
+        </is>
+      </c>
+      <c r="J153" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K153" s="48" t="n"/>
       <c r="L153" s="25">
         <f>IF(D153="","",IF(H153="W",1,IF(H153="L",0,"")))</f>
         <v/>
@@ -11788,13 +11894,51 @@
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="54">
-      <c r="C154" s="50" t="n"/>
-      <c r="D154" s="50" t="n"/>
-      <c r="E154" s="50" t="n"/>
-      <c r="F154" s="50" t="n"/>
-      <c r="G154" s="50" t="n"/>
-      <c r="H154" s="50" t="n"/>
-      <c r="J154" s="50" t="n"/>
+      <c r="A154" s="44" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="42" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C154" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D154" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E154" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F154" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Blaziken ex</t>
+        </is>
+      </c>
+      <c r="G154" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I154" s="44" t="inlineStr">
+        <is>
+          <t>Bad Opening</t>
+        </is>
+      </c>
+      <c r="J154" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K154" s="44" t="n"/>
       <c r="L154" s="25">
         <f>IF(D154="","",IF(H154="W",1,IF(H154="L",0,"")))</f>
         <v/>
@@ -11825,13 +11969,51 @@
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="54">
-      <c r="C155" s="50" t="n"/>
-      <c r="D155" s="50" t="n"/>
-      <c r="E155" s="50" t="n"/>
-      <c r="F155" s="50" t="n"/>
-      <c r="G155" s="50" t="n"/>
-      <c r="H155" s="50" t="n"/>
-      <c r="J155" s="50" t="n"/>
+      <c r="A155" s="48" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C155" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D155" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E155" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F155" s="48" t="inlineStr">
+        <is>
+          <t>Slowking</t>
+        </is>
+      </c>
+      <c r="G155" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I155" s="48" t="inlineStr">
+        <is>
+          <t>Bad Start</t>
+        </is>
+      </c>
+      <c r="J155" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K155" s="48" t="n"/>
       <c r="L155" s="25">
         <f>IF(D155="","",IF(H155="W",1,IF(H155="L",0,"")))</f>
         <v/>
@@ -11862,13 +12044,47 @@
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="54">
-      <c r="C156" s="50" t="n"/>
-      <c r="D156" s="50" t="n"/>
-      <c r="E156" s="50" t="n"/>
-      <c r="F156" s="50" t="n"/>
-      <c r="G156" s="50" t="n"/>
-      <c r="H156" s="50" t="n"/>
-      <c r="J156" s="50" t="n"/>
+      <c r="A156" s="44" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="42" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C156" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D156" s="44" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E156" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F156" s="44" t="inlineStr">
+        <is>
+          <t>Zoroark ex</t>
+        </is>
+      </c>
+      <c r="G156" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I156" s="44" t="n"/>
+      <c r="J156" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K156" s="44" t="n"/>
       <c r="L156" s="25">
         <f>IF(D156="","",IF(H156="W",1,IF(H156="L",0,"")))</f>
         <v/>
@@ -11899,13 +12115,51 @@
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="54">
-      <c r="C157" s="50" t="n"/>
-      <c r="D157" s="50" t="n"/>
-      <c r="E157" s="50" t="n"/>
-      <c r="F157" s="50" t="n"/>
-      <c r="G157" s="50" t="n"/>
-      <c r="H157" s="50" t="n"/>
-      <c r="J157" s="50" t="n"/>
+      <c r="A157" s="48" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C157" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D157" s="48" t="inlineStr">
+        <is>
+          <t>Alakazam Dusknoir</t>
+        </is>
+      </c>
+      <c r="E157" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F157" s="48" t="inlineStr">
+        <is>
+          <t>MegaLucario ex</t>
+        </is>
+      </c>
+      <c r="G157" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I157" s="48" t="n"/>
+      <c r="J157" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K157" s="48" t="inlineStr">
+        <is>
+          <t>ha troppa vita avendo l'energia</t>
+        </is>
+      </c>
       <c r="L157" s="25">
         <f>IF(D157="","",IF(H157="W",1,IF(H157="L",0,"")))</f>
         <v/>
@@ -11936,13 +12190,47 @@
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="54">
-      <c r="C158" s="50" t="n"/>
-      <c r="D158" s="50" t="n"/>
-      <c r="E158" s="50" t="n"/>
-      <c r="F158" s="50" t="n"/>
-      <c r="G158" s="50" t="n"/>
-      <c r="H158" s="50" t="n"/>
-      <c r="J158" s="50" t="n"/>
+      <c r="A158" s="44" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="42" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C158" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E158" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F158" s="44" t="inlineStr">
+        <is>
+          <t>Area Della Festa</t>
+        </is>
+      </c>
+      <c r="G158" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" s="44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I158" s="44" t="n"/>
+      <c r="J158" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K158" s="44" t="n"/>
       <c r="L158" s="25">
         <f>IF(D158="","",IF(H158="W",1,IF(H158="L",0,"")))</f>
         <v/>
@@ -11973,13 +12261,51 @@
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="54">
-      <c r="C159" s="50" t="n"/>
-      <c r="D159" s="50" t="n"/>
-      <c r="E159" s="50" t="n"/>
-      <c r="F159" s="50" t="n"/>
-      <c r="G159" s="50" t="n"/>
-      <c r="H159" s="50" t="n"/>
-      <c r="J159" s="50" t="n"/>
+      <c r="A159" s="48" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="24" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C159" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D159" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E159" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F159" s="48" t="inlineStr">
+        <is>
+          <t>Dhelmise Banette</t>
+        </is>
+      </c>
+      <c r="G159" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" s="48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I159" s="48" t="inlineStr">
+        <is>
+          <t>Lucky Win</t>
+        </is>
+      </c>
+      <c r="J159" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K159" s="48" t="n"/>
       <c r="L159" s="25">
         <f>IF(D159="","",IF(H159="W",1,IF(H159="L",0,"")))</f>
         <v/>
@@ -12010,13 +12336,51 @@
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="54">
-      <c r="C160" s="50" t="n"/>
-      <c r="D160" s="50" t="n"/>
-      <c r="E160" s="50" t="n"/>
-      <c r="F160" s="50" t="n"/>
-      <c r="G160" s="50" t="n"/>
-      <c r="H160" s="50" t="n"/>
-      <c r="J160" s="50" t="n"/>
+      <c r="A160" s="44" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="42" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C160" s="44" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D160" s="44" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E160" s="44" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F160" s="44" t="inlineStr">
+        <is>
+          <t>Area Della Festa</t>
+        </is>
+      </c>
+      <c r="G160" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I160" s="44" t="inlineStr">
+        <is>
+          <t>Bad Draw</t>
+        </is>
+      </c>
+      <c r="J160" s="44" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K160" s="44" t="n"/>
       <c r="L160" s="25">
         <f>IF(D160="","",IF(H160="W",1,IF(H160="L",0,"")))</f>
         <v/>
@@ -12047,13 +12411,51 @@
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="54">
-      <c r="C161" s="50" t="n"/>
-      <c r="D161" s="50" t="n"/>
-      <c r="E161" s="50" t="n"/>
-      <c r="F161" s="50" t="n"/>
-      <c r="G161" s="50" t="n"/>
-      <c r="H161" s="50" t="n"/>
-      <c r="J161" s="50" t="n"/>
+      <c r="A161" s="48" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="24" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C161" s="48" t="inlineStr">
+        <is>
+          <t>TEF-PBL</t>
+        </is>
+      </c>
+      <c r="D161" s="48" t="inlineStr">
+        <is>
+          <t>Dragapult ex Dusknoir</t>
+        </is>
+      </c>
+      <c r="E161" s="48" t="inlineStr">
+        <is>
+          <t>ZamNoir</t>
+        </is>
+      </c>
+      <c r="F161" s="48" t="inlineStr">
+        <is>
+          <t>MegaLopunny ex</t>
+        </is>
+      </c>
+      <c r="G161" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" s="48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I161" s="48" t="inlineStr">
+        <is>
+          <t>Bad Start, Bad Luck</t>
+        </is>
+      </c>
+      <c r="J161" s="48" t="inlineStr">
+        <is>
+          <t>TCGLive</t>
+        </is>
+      </c>
+      <c r="K161" s="48" t="n"/>
       <c r="L161" s="25">
         <f>IF(D161="","",IF(H161="W",1,IF(H161="L",0,"")))</f>
         <v/>
@@ -21552,7 +21954,7 @@
       <formula1>Liste!$F$2:$F$12</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F113 F116:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Liste!$G$2:$G$42</formula1>
+      <formula1>Liste!$G$2:$G$43</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Liste!$C$2:$C$3</formula1>
@@ -21581,7 +21983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z42"/>
+  <dimension ref="A1:Z43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="54" min="1" max="1"/>
@@ -21967,102 +22369,108 @@
     <row r="29" ht="15.75" customHeight="1" s="54">
       <c r="G29" s="50" t="inlineStr">
         <is>
-          <t>MegaSharpedo ex</t>
+          <t>MegaMagnetric ex Eelektrik</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="54">
       <c r="G30" s="50" t="inlineStr">
         <is>
-          <t>MegaStarmie ex Dragapult</t>
+          <t>MegaSharpedo ex</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="54">
       <c r="G31" s="50" t="inlineStr">
         <is>
-          <t>MegaStarmie ex Dusknoir</t>
+          <t>MegaStarmie ex Dragapult</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="54">
       <c r="G32" s="50" t="inlineStr">
         <is>
-          <t>Metagross ex</t>
+          <t>MegaStarmie ex Dusknoir</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="54">
       <c r="G33" s="50" t="inlineStr">
         <is>
-          <t>Mewtwo ex Spidops</t>
+          <t>Metagross ex</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="54">
       <c r="G34" s="50" t="inlineStr">
         <is>
-          <t>Pikachu ex box</t>
+          <t>Mewtwo ex Spidops</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="54">
       <c r="G35" s="50" t="inlineStr">
         <is>
-          <t>Raging Bolt</t>
+          <t>Pikachu ex box</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="54">
       <c r="G36" s="50" t="inlineStr">
         <is>
-          <t>Slowking</t>
+          <t>Raging Bolt</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="54">
       <c r="G37" s="50" t="inlineStr">
         <is>
-          <t>Spineferree ex Bastiodon</t>
+          <t>Slowking</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="54">
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>Toucannon Dusknoir</t>
+          <t>Spineferree ex Bastiodon</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="54">
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>Toxtricity box</t>
+          <t>Toucannon Dusknoir</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="54">
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>Typhlosion</t>
+          <t>Toxtricity box</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="54">
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>Vileplume ex Ogerpon</t>
+          <t>Typhlosion</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="54">
       <c r="G42" s="0" t="inlineStr">
         <is>
+          <t>Vileplume ex Ogerpon</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="54">
+      <c r="G43" s="0" t="inlineStr">
+        <is>
           <t>Zoroark ex</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="54"/>
     <row r="44" ht="15.75" customHeight="1" s="54"/>
     <row r="45" ht="15.75" customHeight="1" s="54"/>
     <row r="46" ht="15.75" customHeight="1" s="54"/>
